--- a/KT_Session_Question_Analysis/00_Drafts/SHRSS_Adobe_KT_Session_Follow_Up_Tracker_SCRATCH.xlsx
+++ b/KT_Session_Question_Analysis/00_Drafts/SHRSS_Adobe_KT_Session_Follow_Up_Tracker_SCRATCH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lambert/Documents/Projects/SHRSS/SHRSS_Knowledge_Transfer/KT_Session_Question_Analysis/00_Drafts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4134D12C-D266-0B4C-A9EA-4125C51FB3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B56E1F-4A62-8442-87B6-582D5AA49068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4960" yWindow="780" windowWidth="28060" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4960" yWindow="760" windowWidth="28060" windowHeight="21580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cursor_Generated" sheetId="12" r:id="rId1"/>
@@ -3131,484 +3131,507 @@
     </row>
     <row r="2" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="G2" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>192</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="G3" t="s">
-        <v>311</v>
+        <v>123</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>313</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>337</v>
-      </c>
-      <c r="E4" t="s">
-        <v>337</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="G4" t="s">
-        <v>311</v>
+        <v>123</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>346</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>357</v>
-      </c>
-      <c r="E5" t="s">
-        <v>357</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="G5" t="s">
-        <v>311</v>
+        <v>123</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>366</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>357</v>
-      </c>
-      <c r="E6" t="s">
-        <v>357</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="G6" t="s">
-        <v>311</v>
+        <v>123</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>373</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>387</v>
+        <v>202</v>
       </c>
       <c r="E7" t="s">
-        <v>387</v>
+        <v>202</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>311</v>
+        <v>11</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>393</v>
+        <v>210</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>394</v>
+        <v>211</v>
       </c>
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>412</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>8</v>
+        <v>415</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>10</v>
+        <v>202</v>
+      </c>
+      <c r="F8" t="s">
+        <v>91</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>25</v>
+        <v>214</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>26</v>
+        <v>215</v>
       </c>
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>412</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>415</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>41</v>
+        <v>216</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>43</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>412</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
+        <v>415</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>202</v>
+      </c>
+      <c r="E10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
       <c r="G10" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3" t="s">
-        <v>406</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>412</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>8</v>
+        <v>415</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>202</v>
+      </c>
+      <c r="E11" t="s">
+        <v>202</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
       <c r="G11" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3" t="s">
-        <v>407</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>412</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>8</v>
+        <v>415</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>202</v>
+      </c>
+      <c r="E12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
       <c r="G12" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3" t="s">
-        <v>408</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>412</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>8</v>
+        <v>415</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>202</v>
+      </c>
+      <c r="E13" t="s">
+        <v>202</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3" t="s">
-        <v>409</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>412</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>8</v>
+        <v>415</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>202</v>
+      </c>
+      <c r="E14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
-        <v>410</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>202</v>
+      </c>
+      <c r="E15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="I15" s="3"/>
+        <v>251</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>202</v>
+      </c>
+      <c r="E16" t="s">
+        <v>202</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="I16" s="3"/>
+        <v>253</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>202</v>
+      </c>
+      <c r="E17" t="s">
+        <v>202</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="I17" s="3"/>
+        <v>255</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>256</v>
+      </c>
       <c r="J17" s="3" t="s">
-        <v>405</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>202</v>
+      </c>
+      <c r="E18" t="s">
+        <v>202</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="I18" s="3"/>
+        <v>258</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>259</v>
+      </c>
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>202</v>
+      </c>
+      <c r="E19" t="s">
+        <v>202</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+        <v>265</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20">
@@ -3618,19 +3641,29 @@
         <v>415</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
         <v>202</v>
       </c>
+      <c r="E20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
       <c r="G20" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
+        <v>207</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21">
@@ -3640,18 +3673,26 @@
         <v>415</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
         <v>202</v>
       </c>
+      <c r="E21" t="s">
+        <v>202</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="I21" s="3"/>
+        <v>247</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>248</v>
+      </c>
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
@@ -3662,19 +3703,29 @@
         <v>415</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
         <v>202</v>
       </c>
+      <c r="E22" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
       <c r="G22" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+        <v>262</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23">
@@ -3684,18 +3735,26 @@
         <v>415</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
         <v>202</v>
       </c>
+      <c r="E23" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
       <c r="G23" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="I23" s="3"/>
+        <v>212</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
@@ -3706,1028 +3765,1075 @@
         <v>415</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
         <v>202</v>
       </c>
+      <c r="E24" t="s">
+        <v>202</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
       <c r="G24" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="I24" s="3"/>
+        <v>220</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>273</v>
+        <v>202</v>
+      </c>
+      <c r="E25" t="s">
+        <v>202</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="I25" s="3"/>
+        <v>222</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>273</v>
+        <v>202</v>
+      </c>
+      <c r="E26" t="s">
+        <v>202</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
+        <v>224</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>273</v>
+        <v>202</v>
+      </c>
+      <c r="E27" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="I27" s="3"/>
+        <v>231</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>202</v>
+      </c>
+      <c r="E28" t="s">
+        <v>202</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
       </c>
       <c r="G28" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="I28" s="3"/>
+        <v>233</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>202</v>
+      </c>
+      <c r="E29" t="s">
+        <v>202</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
+        <v>240</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="30" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>308</v>
+        <v>202</v>
+      </c>
+      <c r="E30" t="s">
+        <v>202</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="I30" s="3"/>
+        <v>245</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>322</v>
+        <v>202</v>
+      </c>
+      <c r="E31" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="I31" s="3"/>
+        <v>249</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="J31" s="3"/>
     </row>
     <row r="32" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D32" t="s">
-        <v>337</v>
+        <v>202</v>
+      </c>
+      <c r="E32" t="s">
+        <v>202</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I32" s="3"/>
+        <v>260</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C33" t="s">
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>357</v>
+        <v>202</v>
+      </c>
+      <c r="E33" t="s">
+        <v>202</v>
+      </c>
+      <c r="F33" t="s">
+        <v>203</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>384</v>
+        <v>204</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="J33" s="3"/>
+        <v>205</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="34" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>357</v>
+        <v>202</v>
+      </c>
+      <c r="E34" t="s">
+        <v>202</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>385</v>
+        <v>235</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="J34" s="3"/>
+        <v>236</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="35" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>387</v>
+        <v>291</v>
       </c>
       <c r="G35" t="s">
         <v>123</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>403</v>
+        <v>306</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
     </row>
     <row r="36" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>387</v>
+        <v>291</v>
       </c>
       <c r="G36" t="s">
         <v>123</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>404</v>
+        <v>307</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>291</v>
       </c>
       <c r="E37" t="s">
-        <v>130</v>
+        <v>291</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>298</v>
       </c>
       <c r="G37" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>175</v>
+        <v>304</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>177</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="J37" s="3"/>
     </row>
     <row r="38" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>412</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>8</v>
+        <v>417</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>9</v>
+        <v>291</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>10</v>
+        <v>291</v>
+      </c>
+      <c r="F38" t="s">
+        <v>193</v>
       </c>
       <c r="G38" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>12</v>
+        <v>292</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>13</v>
+        <v>293</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>14</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>412</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>15</v>
+        <v>417</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>291</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>10</v>
+        <v>291</v>
+      </c>
+      <c r="F39" t="s">
+        <v>193</v>
       </c>
       <c r="G39" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
       <c r="J39" s="3"/>
     </row>
     <row r="40" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>412</v>
-      </c>
-      <c r="C40" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>9</v>
+        <v>291</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>10</v>
+        <v>291</v>
+      </c>
+      <c r="F40" t="s">
+        <v>295</v>
       </c>
       <c r="G40" t="s">
-        <v>11</v>
+        <v>193</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>23</v>
+        <v>297</v>
       </c>
       <c r="J40" s="3"/>
     </row>
     <row r="41" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>412</v>
-      </c>
-      <c r="C41" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C41" t="s">
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>9</v>
+        <v>291</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>10</v>
+        <v>291</v>
+      </c>
+      <c r="F41" t="s">
+        <v>298</v>
       </c>
       <c r="G41" t="s">
-        <v>11</v>
+        <v>193</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>27</v>
+        <v>299</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c r="J41" s="3"/>
     </row>
     <row r="42" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>412</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>15</v>
+        <v>414</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F42" t="s">
         <v>10</v>
       </c>
       <c r="G42" t="s">
-        <v>11</v>
+        <v>189</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J42" s="3"/>
+        <v>191</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="43" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>412</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>15</v>
+        <v>414</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="G43" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>32</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="I43" s="3"/>
       <c r="J43" s="3"/>
     </row>
     <row r="44" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>412</v>
-      </c>
-      <c r="C44" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C44" t="s">
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="G44" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>38</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
     </row>
     <row r="45" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>412</v>
-      </c>
-      <c r="C45" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C45" t="s">
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="G45" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>51</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>52</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>412</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>61</v>
+        <v>414</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="G46" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
     </row>
     <row r="47" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>412</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>15</v>
+        <v>414</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="G47" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>68</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="I47" s="3"/>
       <c r="J47" s="3"/>
     </row>
     <row r="48" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>412</v>
-      </c>
-      <c r="C48" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C48" t="s">
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F48" t="s">
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>11</v>
+        <v>174</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>412</v>
-      </c>
-      <c r="C49" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C49" t="s">
         <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F49" t="s">
         <v>10</v>
       </c>
       <c r="G49" t="s">
         <v>11</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J49" s="3"/>
+        <v>151</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="50" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>412</v>
-      </c>
-      <c r="C50" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C50" t="s">
         <v>61</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F50" t="s">
         <v>10</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>81</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="J50" s="3"/>
     </row>
     <row r="51" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>412</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>61</v>
+        <v>414</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
+      </c>
+      <c r="F51" t="s">
+        <v>171</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>84</v>
+        <v>172</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>85</v>
+        <v>173</v>
       </c>
       <c r="J51" s="3"/>
     </row>
     <row r="52" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>412</v>
-      </c>
-      <c r="C52" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C52" t="s">
         <v>61</v>
       </c>
       <c r="D52" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F52" t="s">
         <v>10</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>88</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="J52" s="3"/>
     </row>
     <row r="53" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>412</v>
-      </c>
-      <c r="C53" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C53" t="s">
         <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F53" t="s">
         <v>10</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="J53" s="3"/>
     </row>
     <row r="54" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>412</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>8</v>
+        <v>414</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>91</v>
+        <v>130</v>
+      </c>
+      <c r="F54" t="s">
+        <v>10</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>94</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="J54" s="3"/>
     </row>
     <row r="55" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>412</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>15</v>
+        <v>414</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
+      </c>
+      <c r="F55" t="s">
+        <v>193</v>
       </c>
       <c r="G55" t="s">
-        <v>11</v>
+        <v>194</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>97</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="J55" s="3"/>
     </row>
     <row r="56" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>412</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>8</v>
+        <v>414</v>
+      </c>
+      <c r="C56" t="s">
+        <v>61</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F56" t="s">
         <v>10</v>
       </c>
       <c r="G56" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>412</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>61</v>
+        <v>414</v>
+      </c>
+      <c r="C57" t="s">
+        <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
+      </c>
+      <c r="F57" t="s">
+        <v>131</v>
       </c>
       <c r="G57" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J57" s="3"/>
+        <v>163</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="58" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>412</v>
-      </c>
-      <c r="C58" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C58" t="s">
         <v>15</v>
       </c>
       <c r="D58" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F58" t="s">
         <v>10</v>
       </c>
       <c r="G58" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>109</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>412</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>8</v>
+        <v>414</v>
+      </c>
+      <c r="C59" t="s">
+        <v>61</v>
       </c>
       <c r="D59" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>91</v>
+        <v>130</v>
+      </c>
+      <c r="F59" t="s">
+        <v>10</v>
       </c>
       <c r="G59" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J59" s="3"/>
+        <v>136</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="60" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B60" t="s">
-        <v>412</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>8</v>
+        <v>414</v>
+      </c>
+      <c r="C60" t="s">
+        <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
+      </c>
+      <c r="F60" t="s">
+        <v>10</v>
       </c>
       <c r="G60" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J60" s="3"/>
     </row>
@@ -4739,7 +4845,7 @@
         <v>414</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D61" t="s">
         <v>130</v>
@@ -4751,17 +4857,15 @@
         <v>10</v>
       </c>
       <c r="G61" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>152</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="J61" s="3"/>
     </row>
     <row r="62" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62">
@@ -4783,15 +4887,17 @@
         <v>10</v>
       </c>
       <c r="G62" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J62" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="63" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63">
@@ -4801,7 +4907,7 @@
         <v>414</v>
       </c>
       <c r="C63" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
         <v>130</v>
@@ -4810,18 +4916,20 @@
         <v>130</v>
       </c>
       <c r="F63" t="s">
-        <v>171</v>
+        <v>10</v>
       </c>
       <c r="G63" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="J63" s="3"/>
+        <v>146</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="64" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64">
@@ -4843,13 +4951,13 @@
         <v>10</v>
       </c>
       <c r="G64" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="J64" s="3"/>
     </row>
@@ -4873,15 +4981,17 @@
         <v>10</v>
       </c>
       <c r="G65" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J65" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="66" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66">
@@ -4903,721 +5013,698 @@
         <v>10</v>
       </c>
       <c r="G66" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J66" s="3"/>
     </row>
     <row r="67" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C67" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D67" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="E67" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="F67" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G67" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J67" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="68" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C68" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="E68" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="F68" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="G68" t="s">
-        <v>11</v>
+        <v>157</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="J68" s="3"/>
     </row>
     <row r="69" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C69" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="E69" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="F69" t="s">
         <v>10</v>
       </c>
       <c r="G69" t="s">
-        <v>11</v>
+        <v>157</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J69" s="3"/>
+        <v>187</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="70" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>415</v>
-      </c>
-      <c r="C70" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D70" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>202</v>
-      </c>
-      <c r="F70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G70" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>218</v>
+        <v>25</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="J70" s="3"/>
     </row>
     <row r="71" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B71" t="s">
-        <v>415</v>
-      </c>
-      <c r="C71" t="s">
+        <v>412</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>202</v>
-      </c>
-      <c r="F71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G71" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>227</v>
+        <v>41</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J71" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="72" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>415</v>
-      </c>
-      <c r="C72" t="s">
-        <v>15</v>
+        <v>412</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>202</v>
-      </c>
-      <c r="E72" t="s">
-        <v>202</v>
-      </c>
-      <c r="F72" t="s">
-        <v>10</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F72" s="3"/>
       <c r="G72" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="J72" s="3"/>
+        <v>124</v>
+      </c>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="73" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>415</v>
-      </c>
-      <c r="C73" t="s">
-        <v>15</v>
+        <v>412</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D73" t="s">
-        <v>202</v>
-      </c>
-      <c r="E73" t="s">
-        <v>202</v>
-      </c>
-      <c r="F73" t="s">
-        <v>10</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F73" s="3"/>
       <c r="G73" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="J73" s="3"/>
+        <v>126</v>
+      </c>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="74" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>415</v>
-      </c>
-      <c r="C74" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D74" t="s">
-        <v>202</v>
-      </c>
-      <c r="E74" t="s">
-        <v>202</v>
-      </c>
-      <c r="F74" t="s">
-        <v>10</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F74" s="3"/>
       <c r="G74" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="J74" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="75" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B75" t="s">
-        <v>415</v>
-      </c>
-      <c r="C75" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D75" t="s">
-        <v>202</v>
-      </c>
-      <c r="E75" t="s">
-        <v>202</v>
-      </c>
-      <c r="F75" t="s">
-        <v>10</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F75" s="3"/>
       <c r="G75" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J75" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="76" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>415</v>
-      </c>
-      <c r="C76" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D76" t="s">
-        <v>202</v>
-      </c>
-      <c r="E76" t="s">
-        <v>202</v>
-      </c>
-      <c r="F76" t="s">
-        <v>10</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F76" s="3"/>
       <c r="G76" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="J76" s="3"/>
+        <v>129</v>
+      </c>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="77" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>415</v>
-      </c>
-      <c r="C77" t="s">
-        <v>15</v>
+        <v>412</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D77" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>202</v>
-      </c>
-      <c r="F77" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G77" t="s">
         <v>11</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>255</v>
+        <v>12</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>256</v>
+        <v>13</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>257</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>415</v>
-      </c>
-      <c r="C78" t="s">
+        <v>412</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>202</v>
-      </c>
-      <c r="F78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G78" t="s">
         <v>11</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>258</v>
+        <v>16</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>259</v>
+        <v>17</v>
       </c>
       <c r="J78" s="3"/>
     </row>
     <row r="79" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>415</v>
-      </c>
-      <c r="C79" t="s">
+        <v>412</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>202</v>
-      </c>
-      <c r="F79" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G79" t="s">
         <v>11</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>265</v>
+        <v>22</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>267</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="J79" s="3"/>
     </row>
     <row r="80" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>414</v>
-      </c>
-      <c r="C80" t="s">
-        <v>8</v>
+        <v>412</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>130</v>
-      </c>
-      <c r="F80" t="s">
-        <v>193</v>
+        <v>9</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G80" t="s">
-        <v>194</v>
+        <v>11</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>195</v>
+        <v>27</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="J80" s="3"/>
     </row>
     <row r="81" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>421</v>
-      </c>
-      <c r="C81" t="s">
-        <v>8</v>
+        <v>412</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>357</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>357</v>
-      </c>
-      <c r="F81" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G81" t="s">
-        <v>381</v>
+        <v>11</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>382</v>
+        <v>29</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>383</v>
+        <v>30</v>
       </c>
       <c r="J81" s="3"/>
     </row>
     <row r="82" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>414</v>
-      </c>
-      <c r="C82" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>130</v>
-      </c>
-      <c r="F82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G82" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>154</v>
+        <v>31</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>156</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="J82" s="3"/>
     </row>
     <row r="83" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>414</v>
-      </c>
-      <c r="C83" t="s">
+        <v>412</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D83" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>130</v>
-      </c>
-      <c r="F83" t="s">
-        <v>131</v>
+        <v>9</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G83" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>162</v>
+        <v>36</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>163</v>
+        <v>37</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>164</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>414</v>
-      </c>
-      <c r="C84" t="s">
-        <v>15</v>
+        <v>412</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D84" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>130</v>
-      </c>
-      <c r="F84" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G84" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>415</v>
-      </c>
-      <c r="C85" t="s">
-        <v>15</v>
+        <v>412</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="D85" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>202</v>
-      </c>
-      <c r="F85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G85" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>207</v>
+        <v>62</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>208</v>
+        <v>63</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>209</v>
+        <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>415</v>
-      </c>
-      <c r="C86" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>202</v>
-      </c>
-      <c r="F86" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G86" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>247</v>
+        <v>67</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>248</v>
+        <v>68</v>
       </c>
       <c r="J86" s="3"/>
     </row>
     <row r="87" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>415</v>
-      </c>
-      <c r="C87" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>202</v>
-      </c>
-      <c r="F87" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G87" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>262</v>
+        <v>69</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>263</v>
+        <v>70</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>264</v>
+        <v>71</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>420</v>
-      </c>
-      <c r="C88" t="s">
+        <v>412</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>337</v>
+        <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>337</v>
-      </c>
-      <c r="F88" t="s">
-        <v>194</v>
+        <v>9</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G88" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>353</v>
+        <v>77</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>355</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="J88" s="3"/>
     </row>
     <row r="89" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>417</v>
-      </c>
-      <c r="C89" t="s">
-        <v>15</v>
+        <v>412</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="D89" t="s">
-        <v>291</v>
+        <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>291</v>
-      </c>
-      <c r="F89" t="s">
-        <v>298</v>
+        <v>9</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>303</v>
+        <v>11</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>304</v>
+        <v>79</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="J89" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="90" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90">
@@ -5627,7 +5714,7 @@
         <v>412</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D90" t="s">
         <v>9</v>
@@ -5639,17 +5726,15 @@
         <v>10</v>
       </c>
       <c r="G90" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="J90" s="3"/>
     </row>
     <row r="91" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91">
@@ -5659,7 +5744,7 @@
         <v>412</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D91" t="s">
         <v>9</v>
@@ -5671,15 +5756,17 @@
         <v>10</v>
       </c>
       <c r="G91" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J91" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="92" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92">
@@ -5701,13 +5788,13 @@
         <v>10</v>
       </c>
       <c r="G92" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="J92" s="3"/>
     </row>
@@ -5719,7 +5806,7 @@
         <v>412</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D93" t="s">
         <v>9</v>
@@ -5728,19 +5815,19 @@
         <v>9</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="G93" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
@@ -5763,15 +5850,17 @@
         <v>10</v>
       </c>
       <c r="G94" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J94" s="3"/>
+        <v>96</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="95" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95">
@@ -5781,7 +5870,7 @@
         <v>412</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D95" t="s">
         <v>9</v>
@@ -5793,15 +5882,17 @@
         <v>10</v>
       </c>
       <c r="G95" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J95" s="3"/>
+        <v>99</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="96" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96">
@@ -5811,7 +5902,7 @@
         <v>412</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D96" t="s">
         <v>9</v>
@@ -5823,13 +5914,13 @@
         <v>10</v>
       </c>
       <c r="G96" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J96" s="3"/>
     </row>
@@ -5841,7 +5932,7 @@
         <v>412</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
@@ -5853,15 +5944,17 @@
         <v>10</v>
       </c>
       <c r="G97" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J97" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="98" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98">
@@ -5871,7 +5964,7 @@
         <v>412</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
@@ -5880,600 +5973,594 @@
         <v>9</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="G98" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>112</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="J98" s="3"/>
     </row>
     <row r="99" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>414</v>
-      </c>
-      <c r="C99" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D99" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E99" t="s">
-        <v>130</v>
-      </c>
-      <c r="F99" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="G99" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J99" s="3" t="s">
-        <v>137</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J99" s="3"/>
     </row>
     <row r="100" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>414</v>
-      </c>
-      <c r="C100" t="s">
+        <v>412</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E100" t="s">
-        <v>130</v>
-      </c>
-      <c r="F100" t="s">
+        <v>9</v>
+      </c>
+      <c r="F100" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G100" t="s">
         <v>18</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J100" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="101" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>414</v>
-      </c>
-      <c r="C101" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>130</v>
-      </c>
-      <c r="F101" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G101" t="s">
         <v>18</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="J101" s="3"/>
     </row>
     <row r="102" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>414</v>
-      </c>
-      <c r="C102" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>130</v>
-      </c>
-      <c r="F102" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G102" t="s">
         <v>18</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>144</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="J102" s="3"/>
     </row>
     <row r="103" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>414</v>
-      </c>
-      <c r="C103" t="s">
+        <v>412</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D103" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>130</v>
-      </c>
-      <c r="F103" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G103" t="s">
         <v>18</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>414</v>
-      </c>
-      <c r="C104" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>130</v>
-      </c>
-      <c r="F104" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G104" t="s">
         <v>18</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="J104" s="3"/>
     </row>
     <row r="105" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>414</v>
-      </c>
-      <c r="C105" t="s">
-        <v>15</v>
+        <v>412</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="D105" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E105" t="s">
-        <v>130</v>
-      </c>
-      <c r="F105" t="s">
+        <v>9</v>
+      </c>
+      <c r="F105" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G105" t="s">
         <v>18</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>167</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="J105" s="3"/>
     </row>
     <row r="106" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>414</v>
-      </c>
-      <c r="C106" t="s">
+        <v>412</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D106" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>130</v>
-      </c>
-      <c r="F106" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G106" t="s">
         <v>18</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="J106" s="3"/>
     </row>
     <row r="107" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>415</v>
-      </c>
-      <c r="C107" t="s">
+        <v>412</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D107" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>202</v>
-      </c>
-      <c r="F107" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G107" t="s">
         <v>18</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>213</v>
+        <v>106</v>
       </c>
       <c r="J107" s="3"/>
     </row>
     <row r="108" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B108" t="s">
-        <v>415</v>
-      </c>
-      <c r="C108" t="s">
+        <v>412</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D108" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E108" t="s">
-        <v>202</v>
-      </c>
-      <c r="F108" t="s">
+        <v>9</v>
+      </c>
+      <c r="F108" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G108" t="s">
         <v>18</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J108" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="109" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>415</v>
-      </c>
-      <c r="C109" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D109" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>202</v>
-      </c>
-      <c r="F109" t="s">
+        <v>9</v>
+      </c>
+      <c r="F109" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G109" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>222</v>
+        <v>116</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="J109" s="3"/>
     </row>
     <row r="110" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>415</v>
-      </c>
-      <c r="C110" t="s">
-        <v>8</v>
+        <v>412</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>202</v>
-      </c>
-      <c r="F110" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G110" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>224</v>
+        <v>34</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>226</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="J110" s="3"/>
     </row>
     <row r="111" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>415</v>
-      </c>
-      <c r="C111" t="s">
+        <v>412</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D111" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>202</v>
-      </c>
-      <c r="F111" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G111" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="J111" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="112" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B112" t="s">
-        <v>415</v>
-      </c>
-      <c r="C112" t="s">
-        <v>15</v>
+        <v>412</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D112" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>202</v>
-      </c>
-      <c r="F112" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G112" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>233</v>
+        <v>45</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>234</v>
+        <v>46</v>
       </c>
       <c r="J112" s="3"/>
     </row>
     <row r="113" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B113" t="s">
-        <v>415</v>
-      </c>
-      <c r="C113" t="s">
-        <v>8</v>
+        <v>412</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>202</v>
-      </c>
-      <c r="F113" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G113" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>240</v>
+        <v>48</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="J113" s="3" t="s">
-        <v>242</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J113" s="3"/>
     </row>
     <row r="114" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>415</v>
-      </c>
-      <c r="C114" t="s">
-        <v>15</v>
+        <v>412</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D114" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>202</v>
-      </c>
-      <c r="F114" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G114" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>245</v>
+        <v>113</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>246</v>
+        <v>114</v>
       </c>
       <c r="J114" s="3"/>
     </row>
     <row r="115" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B115" t="s">
-        <v>415</v>
-      </c>
-      <c r="C115" t="s">
+        <v>412</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D115" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>202</v>
-      </c>
-      <c r="F115" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G115" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>249</v>
+        <v>54</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="J115" s="3"/>
     </row>
     <row r="116" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B116" t="s">
-        <v>415</v>
-      </c>
-      <c r="C116" t="s">
-        <v>61</v>
+        <v>412</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D116" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>202</v>
-      </c>
-      <c r="F116" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G116" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>260</v>
+        <v>56</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>261</v>
+        <v>57</v>
       </c>
       <c r="J116" s="3"/>
     </row>
     <row r="117" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C117" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D117" t="s">
-        <v>273</v>
+        <v>337</v>
       </c>
       <c r="E117" t="s">
-        <v>273</v>
+        <v>337</v>
       </c>
       <c r="F117" t="s">
-        <v>193</v>
+        <v>10</v>
       </c>
       <c r="G117" t="s">
-        <v>18</v>
+        <v>311</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>277</v>
+        <v>345</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>278</v>
+        <v>346</v>
       </c>
       <c r="J117" s="3"/>
     </row>
@@ -6485,27 +6572,18 @@
         <v>420</v>
       </c>
       <c r="C118" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D118" t="s">
         <v>337</v>
       </c>
-      <c r="E118" t="s">
-        <v>337</v>
-      </c>
-      <c r="F118" t="s">
-        <v>10</v>
-      </c>
       <c r="G118" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="J118" s="3"/>
+        <v>356</v>
+      </c>
+      <c r="I118" s="3"/>
     </row>
     <row r="119" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119">
@@ -6524,18 +6602,20 @@
         <v>337</v>
       </c>
       <c r="F119" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="G119" t="s">
-        <v>18</v>
+        <v>153</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J119" s="3"/>
+        <v>354</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="120" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120">
@@ -6545,7 +6625,7 @@
         <v>420</v>
       </c>
       <c r="C120" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D120" t="s">
         <v>337</v>
@@ -6560,10 +6640,10 @@
         <v>18</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="J120" s="3"/>
     </row>
@@ -6575,7 +6655,7 @@
         <v>420</v>
       </c>
       <c r="C121" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D121" t="s">
         <v>337</v>
@@ -6590,134 +6670,134 @@
         <v>18</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="J121" s="3"/>
     </row>
     <row r="122" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C122" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D122" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="E122" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="F122" t="s">
-        <v>361</v>
+        <v>10</v>
       </c>
       <c r="G122" t="s">
         <v>18</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="J122" s="3" t="s">
-        <v>364</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="J122" s="3"/>
     </row>
     <row r="123" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C123" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D123" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="E123" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="F123" t="s">
-        <v>367</v>
+        <v>10</v>
       </c>
       <c r="G123" t="s">
         <v>18</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="J123" s="3"/>
     </row>
     <row r="124" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C124" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D124" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="E124" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="F124" t="s">
         <v>10</v>
       </c>
       <c r="G124" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="J124" s="3"/>
     </row>
     <row r="125" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C125" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D125" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="E125" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="F125" t="s">
         <v>10</v>
       </c>
       <c r="G125" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="J125" s="3"/>
+        <v>339</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="126" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126">
@@ -6727,7 +6807,7 @@
         <v>421</v>
       </c>
       <c r="C126" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D126" t="s">
         <v>357</v>
@@ -6739,199 +6819,183 @@
         <v>10</v>
       </c>
       <c r="G126" t="s">
-        <v>18</v>
+        <v>311</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="J126" s="3"/>
     </row>
     <row r="127" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>412</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>8</v>
+        <v>421</v>
+      </c>
+      <c r="C127" t="s">
+        <v>61</v>
       </c>
       <c r="D127" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="E127" t="s">
-        <v>9</v>
-      </c>
-      <c r="F127" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F127" t="s">
         <v>10</v>
       </c>
       <c r="G127" t="s">
-        <v>115</v>
+        <v>311</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>116</v>
+        <v>372</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>117</v>
+        <v>373</v>
       </c>
       <c r="J127" s="3"/>
     </row>
     <row r="128" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>412</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>15</v>
+        <v>421</v>
+      </c>
+      <c r="C128" t="s">
+        <v>8</v>
       </c>
       <c r="D128" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" t="s">
-        <v>9</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="G128" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>34</v>
+        <v>384</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="J128" s="3"/>
     </row>
     <row r="129" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B129" t="s">
-        <v>412</v>
-      </c>
-      <c r="C129" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C129" t="s">
         <v>8</v>
       </c>
       <c r="D129" t="s">
-        <v>9</v>
-      </c>
-      <c r="E129" t="s">
-        <v>9</v>
-      </c>
-      <c r="F129" s="3" t="s">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="G129" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>58</v>
+        <v>385</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J129" s="3" t="s">
-        <v>60</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="J129" s="3"/>
     </row>
     <row r="130" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B130" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C130" t="s">
         <v>8</v>
       </c>
       <c r="D130" t="s">
-        <v>130</v>
+        <v>357</v>
       </c>
       <c r="E130" t="s">
-        <v>130</v>
+        <v>357</v>
       </c>
       <c r="F130" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G130" t="s">
-        <v>33</v>
+        <v>381</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>132</v>
+        <v>382</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J130" s="3" t="s">
-        <v>134</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="J130" s="3"/>
     </row>
     <row r="131" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B131" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C131" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D131" t="s">
-        <v>202</v>
+        <v>357</v>
       </c>
       <c r="E131" t="s">
-        <v>202</v>
+        <v>357</v>
       </c>
       <c r="F131" t="s">
-        <v>203</v>
+        <v>361</v>
       </c>
       <c r="G131" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>204</v>
+        <v>362</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>205</v>
+        <v>363</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>206</v>
+        <v>364</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B132" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C132" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D132" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="E132" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="F132" t="s">
-        <v>10</v>
+        <v>367</v>
       </c>
       <c r="G132" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="J132" s="3"/>
     </row>
@@ -6952,128 +7016,126 @@
         <v>357</v>
       </c>
       <c r="F133" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="G133" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="J133" s="3" t="s">
-        <v>378</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="J133" s="3"/>
     </row>
     <row r="134" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B134" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C134" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D134" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="E134" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="F134" t="s">
         <v>10</v>
       </c>
       <c r="G134" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="J134" s="3" t="s">
-        <v>390</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="J134" s="3"/>
     </row>
     <row r="135" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B135" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C135" t="s">
         <v>15</v>
       </c>
       <c r="D135" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="E135" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="F135" t="s">
         <v>10</v>
       </c>
       <c r="G135" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="J135" s="3"/>
     </row>
     <row r="136" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B136" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C136" t="s">
         <v>15</v>
       </c>
       <c r="D136" t="s">
-        <v>130</v>
+        <v>357</v>
       </c>
       <c r="E136" t="s">
-        <v>130</v>
+        <v>357</v>
       </c>
       <c r="F136" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="G136" t="s">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>158</v>
+        <v>376</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J136" s="3"/>
+        <v>377</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="137" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B137" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C137" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>130</v>
+        <v>357</v>
       </c>
       <c r="E137" t="s">
-        <v>130</v>
+        <v>357</v>
       </c>
       <c r="F137" t="s">
         <v>10</v>
@@ -7082,180 +7144,166 @@
         <v>157</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>186</v>
+        <v>358</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>187</v>
+        <v>359</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>188</v>
+        <v>360</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B138" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C138" t="s">
         <v>8</v>
       </c>
       <c r="D138" t="s">
-        <v>308</v>
+        <v>387</v>
       </c>
       <c r="E138" t="s">
-        <v>308</v>
+        <v>387</v>
       </c>
       <c r="F138" t="s">
         <v>10</v>
       </c>
       <c r="G138" t="s">
-        <v>157</v>
+        <v>311</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>309</v>
+        <v>393</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>310</v>
+        <v>394</v>
       </c>
       <c r="J138" s="3"/>
     </row>
     <row r="139" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B139" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C139" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D139" t="s">
-        <v>308</v>
-      </c>
-      <c r="E139" t="s">
-        <v>308</v>
-      </c>
-      <c r="F139" t="s">
-        <v>10</v>
+        <v>387</v>
       </c>
       <c r="G139" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="I139" s="3" t="s">
-        <v>318</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="I139" s="3"/>
       <c r="J139" s="3"/>
     </row>
     <row r="140" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B140" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C140" t="s">
         <v>8</v>
       </c>
       <c r="D140" t="s">
-        <v>308</v>
-      </c>
-      <c r="E140" t="s">
-        <v>308</v>
-      </c>
-      <c r="F140" t="s">
-        <v>10</v>
+        <v>387</v>
       </c>
       <c r="G140" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="I140" s="3" t="s">
-        <v>320</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="I140" s="3"/>
       <c r="J140" s="3"/>
     </row>
     <row r="141" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B141" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C141" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D141" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="E141" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="F141" t="s">
         <v>10</v>
       </c>
       <c r="G141" t="s">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J141" s="3"/>
+        <v>389</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="142" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B142" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C142" t="s">
         <v>15</v>
       </c>
       <c r="D142" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="E142" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="F142" t="s">
         <v>10</v>
       </c>
       <c r="G142" t="s">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="J142" s="3"/>
     </row>
     <row r="143" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B143" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C143" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D143" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="E143" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="F143" t="s">
         <v>10</v>
@@ -7264,28 +7312,28 @@
         <v>157</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>327</v>
+        <v>395</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>328</v>
+        <v>396</v>
       </c>
       <c r="J143" s="3"/>
     </row>
     <row r="144" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B144" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C144" t="s">
         <v>61</v>
       </c>
       <c r="D144" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="E144" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="F144" t="s">
         <v>10</v>
@@ -7294,90 +7342,80 @@
         <v>157</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>332</v>
+        <v>398</v>
       </c>
       <c r="J144" s="3"/>
     </row>
     <row r="145" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B145" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C145" t="s">
         <v>15</v>
       </c>
       <c r="D145" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="E145" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="F145" t="s">
-        <v>10</v>
+        <v>399</v>
       </c>
       <c r="G145" t="s">
-        <v>157</v>
+        <v>400</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="J145" s="3" t="s">
-        <v>360</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="J145" s="3"/>
     </row>
     <row r="146" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C146" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D146" t="s">
-        <v>387</v>
-      </c>
-      <c r="E146" t="s">
-        <v>387</v>
-      </c>
-      <c r="F146" t="s">
-        <v>10</v>
+        <v>322</v>
       </c>
       <c r="G146" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="I146" s="3" t="s">
-        <v>396</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="I146" s="3"/>
       <c r="J146" s="3"/>
     </row>
     <row r="147" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C147" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D147" t="s">
-        <v>387</v>
+        <v>322</v>
       </c>
       <c r="E147" t="s">
-        <v>387</v>
+        <v>322</v>
       </c>
       <c r="F147" t="s">
         <v>10</v>
@@ -7386,322 +7424,304 @@
         <v>157</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>397</v>
+        <v>323</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>398</v>
+        <v>324</v>
       </c>
       <c r="J147" s="3"/>
     </row>
     <row r="148" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B148" t="s">
-        <v>412</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>8</v>
+        <v>419</v>
+      </c>
+      <c r="C148" t="s">
+        <v>15</v>
       </c>
       <c r="D148" t="s">
-        <v>9</v>
+        <v>322</v>
       </c>
       <c r="E148" t="s">
-        <v>9</v>
-      </c>
-      <c r="F148" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F148" t="s">
         <v>10</v>
       </c>
       <c r="G148" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>45</v>
+        <v>325</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>46</v>
+        <v>326</v>
       </c>
       <c r="J148" s="3"/>
     </row>
     <row r="149" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B149" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C149" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D149" t="s">
-        <v>202</v>
+        <v>322</v>
       </c>
       <c r="E149" t="s">
-        <v>202</v>
+        <v>322</v>
       </c>
       <c r="F149" t="s">
         <v>10</v>
       </c>
       <c r="G149" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>235</v>
+        <v>327</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="J149" s="3" t="s">
-        <v>237</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="J149" s="3"/>
     </row>
     <row r="150" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B150" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C150" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D150" t="s">
-        <v>273</v>
+        <v>322</v>
       </c>
       <c r="E150" t="s">
-        <v>273</v>
+        <v>322</v>
       </c>
       <c r="F150" t="s">
-        <v>193</v>
+        <v>10</v>
       </c>
       <c r="G150" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="J150" s="3" t="s">
-        <v>276</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="J150" s="3"/>
     </row>
     <row r="151" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B151" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C151" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D151" t="s">
-        <v>273</v>
+        <v>322</v>
       </c>
       <c r="E151" t="s">
-        <v>273</v>
+        <v>322</v>
       </c>
       <c r="F151" t="s">
-        <v>193</v>
+        <v>10</v>
       </c>
       <c r="G151" t="s">
-        <v>44</v>
+        <v>314</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>279</v>
+        <v>329</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="J151" s="3"/>
     </row>
     <row r="152" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B152" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C152" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D152" t="s">
-        <v>273</v>
+        <v>322</v>
       </c>
       <c r="E152" t="s">
-        <v>273</v>
+        <v>322</v>
       </c>
       <c r="F152" t="s">
-        <v>193</v>
+        <v>10</v>
       </c>
       <c r="G152" t="s">
-        <v>44</v>
+        <v>333</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>281</v>
+        <v>334</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="J152" s="3"/>
     </row>
     <row r="153" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C153" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D153" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="E153" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="F153" t="s">
-        <v>193</v>
+        <v>10</v>
       </c>
       <c r="G153" t="s">
-        <v>44</v>
+        <v>311</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="J153" s="3" t="s">
-        <v>285</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="J153" s="3"/>
     </row>
     <row r="154" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C154" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D154" t="s">
-        <v>273</v>
-      </c>
-      <c r="E154" t="s">
-        <v>273</v>
-      </c>
-      <c r="F154" t="s">
-        <v>193</v>
+        <v>308</v>
       </c>
       <c r="G154" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="I154" s="3" t="s">
-        <v>287</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="I154" s="3"/>
       <c r="J154" s="3"/>
     </row>
     <row r="155" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C155" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D155" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E155" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="F155" t="s">
-        <v>193</v>
+        <v>10</v>
       </c>
       <c r="G155" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="J155" s="3" t="s">
-        <v>294</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="J155" s="3"/>
     </row>
     <row r="156" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B156" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C156" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D156" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E156" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="F156" t="s">
-        <v>193</v>
+        <v>10</v>
       </c>
       <c r="G156" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="J156" s="3"/>
     </row>
     <row r="157" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B157" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C157" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D157" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="E157" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="F157" t="s">
         <v>10</v>
       </c>
       <c r="G157" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="J157" s="3" t="s">
-        <v>340</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="J157" s="3"/>
     </row>
     <row r="158" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158">
@@ -7735,277 +7755,257 @@
     </row>
     <row r="159" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B159" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C159" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D159" t="s">
-        <v>322</v>
-      </c>
-      <c r="E159" t="s">
-        <v>322</v>
-      </c>
-      <c r="F159" t="s">
-        <v>10</v>
+        <v>273</v>
       </c>
       <c r="G159" t="s">
-        <v>314</v>
+        <v>123</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="I159" s="3" t="s">
-        <v>330</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="I159" s="3"/>
       <c r="J159" s="3"/>
     </row>
     <row r="160" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B160" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C160" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D160" t="s">
-        <v>387</v>
-      </c>
-      <c r="E160" t="s">
-        <v>387</v>
-      </c>
-      <c r="F160" t="s">
-        <v>399</v>
+        <v>273</v>
       </c>
       <c r="G160" t="s">
-        <v>400</v>
+        <v>123</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="I160" s="3" t="s">
-        <v>402</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="I160" s="3"/>
       <c r="J160" s="3"/>
     </row>
     <row r="161" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B161" t="s">
-        <v>412</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>15</v>
+        <v>416</v>
+      </c>
+      <c r="C161" t="s">
+        <v>8</v>
       </c>
       <c r="D161" t="s">
-        <v>9</v>
-      </c>
-      <c r="E161" t="s">
-        <v>9</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>10</v>
+        <v>273</v>
       </c>
       <c r="G161" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I161" s="3" t="s">
-        <v>49</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="I161" s="3"/>
       <c r="J161" s="3"/>
     </row>
     <row r="162" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B162" t="s">
-        <v>412</v>
-      </c>
-      <c r="C162" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C162" t="s">
         <v>8</v>
       </c>
       <c r="D162" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="E162" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>10</v>
+        <v>273</v>
+      </c>
+      <c r="F162" t="s">
+        <v>193</v>
       </c>
       <c r="G162" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>113</v>
+        <v>277</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>114</v>
+        <v>278</v>
       </c>
       <c r="J162" s="3"/>
     </row>
     <row r="163" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B163" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C163" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D163" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="E163" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="F163" t="s">
-        <v>10</v>
+        <v>193</v>
       </c>
       <c r="G163" t="s">
-        <v>333</v>
+        <v>44</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>334</v>
+        <v>274</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="J163" s="3"/>
+        <v>275</v>
+      </c>
+      <c r="J163" s="3" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="164" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B164" t="s">
-        <v>412</v>
-      </c>
-      <c r="C164" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C164" t="s">
         <v>8</v>
       </c>
       <c r="D164" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="E164" t="s">
-        <v>9</v>
-      </c>
-      <c r="F164" s="3" t="s">
-        <v>10</v>
+        <v>273</v>
+      </c>
+      <c r="F164" t="s">
+        <v>193</v>
       </c>
       <c r="G164" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>54</v>
+        <v>279</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="J164" s="3"/>
     </row>
     <row r="165" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B165" t="s">
-        <v>412</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>8</v>
+        <v>416</v>
+      </c>
+      <c r="C165" t="s">
+        <v>61</v>
       </c>
       <c r="D165" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="E165" t="s">
-        <v>9</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>10</v>
+        <v>273</v>
+      </c>
+      <c r="F165" t="s">
+        <v>193</v>
       </c>
       <c r="G165" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>56</v>
+        <v>281</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>57</v>
+        <v>282</v>
       </c>
       <c r="J165" s="3"/>
     </row>
     <row r="166" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B166" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C166" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D166" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="E166" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="F166" t="s">
-        <v>295</v>
+        <v>193</v>
       </c>
       <c r="G166" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="J166" s="3"/>
+        <v>284</v>
+      </c>
+      <c r="J166" s="3" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="167" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B167" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C167" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D167" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="E167" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="F167" t="s">
-        <v>298</v>
+        <v>193</v>
       </c>
       <c r="G167" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="J167" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J167">
-    <sortCondition descending="1" ref="G2:G167"/>
+    <sortCondition ref="B2:B167"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
